--- a/jira_export_2026-08-18.xlsx
+++ b/jira_export_2026-08-18.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>226 h</t>
+          <t>271 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P118"/>
+  <dimension ref="A1:P122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1126,27 +1126,27 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-34989</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>[Commune de Villeneuve D'Ascq] - Montée de version Littéralis Expert de 2024.1.0.0 vers 2026.3.0.0 en test et prod (ON-PREM)</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>Montée de version Littéralis Expert de 2024.1.0.0 vers 2026.3.0.0 en test et prod (ON-PREM)</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -1166,23 +1166,23 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="J6" s="14" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-34993</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178306</t>
         </is>
       </c>
       <c r="N6" s="15" t="n">
@@ -1198,12 +1198,12 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34925</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>AME multi-communes acheté par la CC</t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1238,23 +1238,23 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34929</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>00178034</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N7" s="12" t="n">
@@ -1270,27 +1270,27 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34857</t>
+          <t>PDMDEP-34925</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Matching DA/DPA</t>
+          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Matching DA/DPA</t>
+          <t>AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -1310,23 +1310,23 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="J8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="14" t="n">
-        <v>0.25</v>
-      </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34861</t>
+          <t>PDMDEP-34929</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>00177271</t>
+          <t>00178034</t>
         </is>
       </c>
       <c r="N8" s="15" t="n">
@@ -1342,27 +1342,27 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34848</t>
+          <t>PDMDEP-34857</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
+          <t>[COMMUNE DE BIARRITZ] - Matching DA/DPA</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Marine MASINGARBE</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
+          <t>Matching DA/DPA</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -1382,17 +1382,25 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L9" s="11" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34861</t>
+        </is>
+      </c>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>00177271</t>
+        </is>
+      </c>
       <c r="N9" s="12" t="n">
         <v>0</v>
       </c>
@@ -1406,42 +1414,42 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34848</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
+          <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Marine MASINGARBE</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
@@ -1453,23 +1461,15 @@
         <v>1</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34825</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="inlineStr">
-        <is>
-          <t>00177218</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
       <c r="N10" s="15" t="n">
-        <v>2419</v>
+        <v>0</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>2419</v>
+        <v>0</v>
       </c>
       <c r="P10" s="15" t="n">
         <v>0</v>
@@ -1478,27 +1478,27 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -1529,19 +1529,19 @@
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>429.3</v>
-      </c>
-      <c r="O11" s="16" t="n">
-        <v>0</v>
+        <v>2419</v>
+      </c>
+      <c r="O11" s="12" t="n">
+        <v>2419</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
@@ -1550,12 +1550,12 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34694</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Commune du Tampon</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -1585,32 +1585,32 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J12" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34701</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>00176675</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N12" s="15" t="n">
-        <v>789.5</v>
+        <v>429.3</v>
       </c>
       <c r="O12" s="16" t="n">
         <v>0</v>
@@ -1622,32 +1622,32 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
@@ -1673,16 +1673,16 @@
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>495</v>
+        <v>789.5</v>
       </c>
       <c r="O13" s="16" t="n">
         <v>0</v>
@@ -1694,12 +1694,12 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -1734,27 +1734,27 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
-        <v>1892</v>
+        <v>495</v>
       </c>
       <c r="O14" s="16" t="n">
         <v>0</v>
@@ -1766,27 +1766,27 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34521</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[Commune de La Flèche] - Migration GEODP Placier et ODP</t>
+          <t>[COMMUNE DE FRONTON] - Simple commande de Pax pour installer Placier dessus</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>COMMUNE DE FRONTON</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>Simple commande de Pax pour installer Placier dessus</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1801,34 +1801,34 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34527</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00173007</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>895</v>
-      </c>
-      <c r="O15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="12" t="n">
@@ -1838,32 +1838,32 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34337</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Commune de Chalons-sur-Saone</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Achat nouveau PAX A920</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1878,30 +1878,30 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34345</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00171711</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="15" t="n">
-        <v>50</v>
+        <v>1892</v>
+      </c>
+      <c r="O16" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P16" s="15" t="n">
         <v>0</v>
@@ -1910,27 +1910,27 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[Commune de La Flèche] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1950,27 +1950,27 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>769.5</v>
+        <v>895</v>
       </c>
       <c r="O17" s="16" t="n">
         <v>0</v>
@@ -1982,27 +1982,27 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
@@ -2033,19 +2033,19 @@
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34345</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171711</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O18" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O18" s="15" t="n">
+        <v>50</v>
       </c>
       <c r="P18" s="15" t="n">
         <v>0</v>
@@ -2054,32 +2054,32 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>4536</v>
+        <v>769.5</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>0</v>
@@ -2126,27 +2126,27 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
@@ -2177,19 +2177,19 @@
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>525</v>
+        <v>2127.2</v>
       </c>
       <c r="O20" s="16" t="n">
-        <v>367.5</v>
+        <v>0</v>
       </c>
       <c r="P20" s="15" t="n">
         <v>0</v>
@@ -2198,32 +2198,32 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1662</v>
+        <v>4536</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2270,42 +2270,42 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34183</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MEGEVE</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
@@ -2317,15 +2317,23 @@
         <v>2</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L22" s="14" t="inlineStr"/>
-      <c r="M22" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34216</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="inlineStr">
+        <is>
+          <t>00171155</t>
+        </is>
+      </c>
       <c r="N22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="15" t="n">
-        <v>0</v>
+        <v>525</v>
+      </c>
+      <c r="O22" s="16" t="n">
+        <v>367.5</v>
       </c>
       <c r="P22" s="15" t="n">
         <v>0</v>
@@ -2334,27 +2342,27 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2369,12 +2377,12 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
@@ -2385,16 +2393,16 @@
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>0</v>
@@ -2406,69 +2414,61 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34117</t>
-        </is>
-      </c>
-      <c r="M24" s="14" t="inlineStr">
-        <is>
-          <t>00170907</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L24" s="14" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
       <c r="N24" s="15" t="n">
-        <v>707</v>
-      </c>
-      <c r="O24" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="15" t="n">
@@ -2478,12 +2478,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2493,12 +2493,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2513,32 +2513,32 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>300</v>
+        <v>9623.1</v>
       </c>
       <c r="O25" s="16" t="n">
         <v>0</v>
@@ -2550,27 +2550,27 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
@@ -2601,16 +2601,16 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>510</v>
+        <v>707</v>
       </c>
       <c r="O26" s="16" t="n">
         <v>0</v>
@@ -2622,32 +2622,32 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2662,27 +2662,27 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>9.75</v>
+        <v>0.25</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>242.9</v>
+        <v>300</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2694,32 +2694,32 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2729,32 +2729,32 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>220</v>
+        <v>510</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2766,32 +2766,32 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2801,34 +2801,34 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0.25</v>
+        <v>9.75</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="12" t="n">
+        <v>242.9</v>
+      </c>
+      <c r="O29" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="12" t="n">
@@ -2838,32 +2838,32 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
@@ -2889,16 +2889,16 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>680</v>
+        <v>220</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2910,32 +2910,32 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Installation serveurs et montée de version TEST ET PROD</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2945,34 +2945,34 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="O31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="12" t="n">
@@ -2982,32 +2982,32 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -3017,49 +3017,49 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="15" t="n">
-        <v>416.29</v>
+        <v>680</v>
+      </c>
+      <c r="O32" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P32" s="15" t="n">
-        <v>47.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -3069,12 +3069,12 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3101,20 +3101,20 @@
         <v>2</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1890</v>
+        <v>787.5</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3126,27 +3126,27 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3166,64 +3166,64 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>920</v>
-      </c>
-      <c r="O34" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O34" s="15" t="n">
+        <v>416.29</v>
       </c>
       <c r="P34" s="15" t="n">
-        <v>0</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -3233,32 +3233,32 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>4040</v>
+        <v>1890</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3270,32 +3270,32 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3310,27 +3310,27 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>1017.5</v>
+        <v>920</v>
       </c>
       <c r="O36" s="16" t="n">
         <v>0</v>
@@ -3342,27 +3342,27 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33638</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>COMMUNE DE MOULINS</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>Migration GeODP Placier et MEP module Caisse</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3377,34 +3377,34 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33647</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00169251</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>1416</v>
-      </c>
-      <c r="O37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="12" t="n">
@@ -3414,32 +3414,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3449,32 +3449,32 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>171.4</v>
+        <v>4040</v>
       </c>
       <c r="O38" s="16" t="n">
         <v>0</v>
@@ -3486,27 +3486,27 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3521,32 +3521,32 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>4174</v>
+        <v>1017.5</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3558,27 +3558,27 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
@@ -3609,16 +3609,16 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>344</v>
+        <v>1416</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3630,12 +3630,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3670,27 +3670,27 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>514.2</v>
+        <v>171.4</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3702,27 +3702,27 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
@@ -3753,16 +3753,16 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3774,32 +3774,32 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3809,32 +3809,32 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>149</v>
+        <v>514.2</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3846,32 +3846,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3886,27 +3886,27 @@
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3918,32 +3918,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3953,34 +3953,34 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="12" t="n">
+        <v>149</v>
+      </c>
+      <c r="O45" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="12" t="n">
@@ -3990,32 +3990,32 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4025,69 +4025,69 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>1.5</v>
+        <v>4.12</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>910</v>
-      </c>
-      <c r="O46" s="15" t="n">
-        <v>910</v>
+        <v>625</v>
+      </c>
+      <c r="O46" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P46" s="15" t="n">
-        <v>606.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4097,34 +4097,34 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P47" s="12" t="n">
@@ -4134,27 +4134,27 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4174,64 +4174,64 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>323.7</v>
+        <v>910</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>1294.8</v>
+        <v>455</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4257,16 +4257,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4278,27 +4278,27 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4318,59 +4318,59 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>400</v>
-      </c>
-      <c r="O50" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O50" s="15" t="n">
+        <v>323.7</v>
       </c>
       <c r="P50" s="15" t="n">
-        <v>0</v>
+        <v>1294.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4390,93 +4390,101 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>1294.224</v>
+        <v>500</v>
       </c>
       <c r="O51" s="16" t="n">
-        <v>219.36</v>
+        <v>0</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>79.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L52" s="14" t="inlineStr"/>
-      <c r="M52" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L52" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-32974</t>
+        </is>
+      </c>
+      <c r="M52" s="14" t="inlineStr">
+        <is>
+          <t>00165260</t>
+        </is>
+      </c>
       <c r="N52" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="O52" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="15" t="n">
@@ -4486,12 +4494,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -4501,12 +4509,12 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4526,101 +4534,93 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>142.1</v>
+        <v>1294.224</v>
       </c>
       <c r="O53" s="16" t="n">
-        <v>0</v>
+        <v>219.36</v>
       </c>
       <c r="P53" s="12" t="n">
-        <v>0</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-32470</t>
-        </is>
-      </c>
-      <c r="M54" s="14" t="inlineStr">
-        <is>
-          <t>00161950</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L54" s="14" t="inlineStr"/>
+      <c r="M54" s="14" t="inlineStr"/>
       <c r="N54" s="15" t="n">
-        <v>2335</v>
-      </c>
-      <c r="O54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="15" t="n">
@@ -4630,32 +4630,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4665,32 +4665,32 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>450</v>
+        <v>142.1</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4702,32 +4702,32 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4737,32 +4737,32 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>910</v>
+        <v>2335</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4774,23 +4774,27 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C57" s="11" t="inlineStr"/>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4810,7 +4814,7 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
@@ -4821,16 +4825,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>255</v>
+        <v>450</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4842,32 +4846,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4877,64 +4881,60 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="15" t="n">
-        <v>100</v>
+        <v>910</v>
+      </c>
+      <c r="O58" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
-        </is>
-      </c>
-      <c r="C59" s="11" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr"/>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4949,12 +4949,12 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
@@ -4965,16 +4965,16 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>590.15</v>
+        <v>255</v>
       </c>
       <c r="O59" s="16" t="n">
         <v>0</v>
@@ -4986,27 +4986,27 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5026,64 +5026,64 @@
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O60" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O60" s="15" t="n">
+        <v>100</v>
       </c>
       <c r="P60" s="15" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5098,29 +5098,29 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="n">
+        <v>590.15</v>
+      </c>
+      <c r="O61" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5130,12 +5130,12 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
@@ -5181,16 +5181,16 @@
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>285</v>
+        <v>1000</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5202,12 +5202,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5237,34 +5237,34 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>1325</v>
-      </c>
-      <c r="O63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
@@ -5274,32 +5274,32 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
@@ -5325,16 +5325,16 @@
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O64" s="16" t="n">
         <v>0</v>
@@ -5346,32 +5346,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
@@ -5397,16 +5397,16 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>588</v>
+        <v>1325</v>
       </c>
       <c r="O65" s="16" t="n">
         <v>0</v>
@@ -5418,32 +5418,32 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -5453,32 +5453,32 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K66" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>203.5</v>
+        <v>120</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5490,27 +5490,27 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5530,27 +5530,27 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K67" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>300</v>
+        <v>588</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5562,32 +5562,32 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -5597,32 +5597,32 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>700</v>
+        <v>203.5</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5634,61 +5634,69 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L69" s="11" t="inlineStr"/>
-      <c r="M69" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L69" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31596</t>
+        </is>
+      </c>
+      <c r="M69" s="11" t="inlineStr">
+        <is>
+          <t>00157967</t>
+        </is>
+      </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="O69" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5698,27 +5706,27 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5738,27 +5746,27 @@
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>4</v>
+        <v>11.75</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>416.475</v>
+        <v>700</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5770,69 +5778,61 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31360</t>
-        </is>
-      </c>
-      <c r="M71" s="11" t="inlineStr">
-        <is>
-          <t>00157041</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L71" s="11" t="inlineStr"/>
+      <c r="M71" s="11" t="inlineStr"/>
       <c r="N71" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="O71" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -5842,32 +5842,32 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -5877,32 +5877,32 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>281</v>
+        <v>416.475</v>
       </c>
       <c r="O72" s="16" t="n">
         <v>0</v>
@@ -5914,12 +5914,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
@@ -5965,16 +5965,16 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -5986,12 +5986,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
@@ -6037,16 +6037,16 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6058,12 +6058,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
@@ -6098,27 +6098,27 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K75" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6130,32 +6130,32 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6165,32 +6165,32 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>690</v>
+        <v>255</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6202,32 +6202,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6237,28 +6237,28 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
@@ -6274,32 +6274,32 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -6309,32 +6309,32 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>187.5</v>
+        <v>140</v>
       </c>
       <c r="O78" s="16" t="n">
         <v>0</v>
@@ -6346,27 +6346,27 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6386,27 +6386,27 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>787.5</v>
+        <v>690</v>
       </c>
       <c r="O79" s="16" t="n">
         <v>0</v>
@@ -6418,32 +6418,32 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -6453,34 +6453,34 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>725</v>
-      </c>
-      <c r="O80" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
@@ -6490,26 +6490,28 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
@@ -6523,34 +6525,34 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="12" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="O81" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -6560,27 +6562,27 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
@@ -6595,34 +6597,34 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0.1</v>
+        <v>2.25</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="15" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="O82" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
@@ -6632,32 +6634,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6667,34 +6669,34 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="O83" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6704,12 +6706,12 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
@@ -6719,13 +6721,11 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E84" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="n">
+        <v/>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -6744,23 +6744,23 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
@@ -6899,18 +6899,18 @@
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O86" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="15" t="n">
@@ -6920,12 +6920,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6935,11 +6935,13 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
@@ -6958,23 +6960,23 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
@@ -6990,12 +6992,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -7005,11 +7007,13 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E88" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -7028,29 +7032,29 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O88" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7060,22 +7064,22 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
@@ -7100,29 +7104,29 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O89" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -7132,12 +7136,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7147,13 +7151,11 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
-        </is>
-      </c>
-      <c r="E90" s="14" t="inlineStr">
-        <is>
-          <t>Script purge de données</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="n">
+        <v/>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
@@ -7162,27 +7164,35 @@
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L90" s="14" t="inlineStr"/>
-      <c r="M90" s="14" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="L90" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27557</t>
+        </is>
+      </c>
+      <c r="M90" s="14" t="inlineStr">
+        <is>
+          <t>00144532</t>
+        </is>
+      </c>
       <c r="N90" s="15" t="n">
         <v>0</v>
       </c>
@@ -7196,22 +7206,22 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -7234,29 +7244,29 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="12" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O91" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="12" t="n">
@@ -7266,12 +7276,12 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
@@ -7281,11 +7291,13 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E92" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
@@ -7304,23 +7316,23 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
@@ -7336,12 +7348,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7351,11 +7363,13 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
@@ -7364,35 +7378,27 @@
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28055</t>
-        </is>
-      </c>
-      <c r="M93" s="11" t="inlineStr">
-        <is>
-          <t>499132</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L93" s="11" t="inlineStr"/>
+      <c r="M93" s="11" t="inlineStr"/>
       <c r="N93" s="12" t="n">
         <v>0</v>
       </c>
@@ -7406,22 +7412,22 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
@@ -7444,23 +7450,23 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
@@ -7476,22 +7482,22 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7514,23 +7520,23 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>1.19</v>
+        <v>0.5</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
@@ -7546,12 +7552,12 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
@@ -7561,7 +7567,7 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7584,23 +7590,23 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
@@ -7616,12 +7622,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7631,7 +7637,7 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7654,23 +7660,23 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>13</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>1.19</v>
+        <v>0.25</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
@@ -7735,12 +7741,12 @@
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
@@ -7756,22 +7762,22 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7789,34 +7795,34 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.5</v>
+        <v>1.19</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O99" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7826,12 +7832,12 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -7841,7 +7847,7 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
@@ -7857,20 +7863,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H100" s="14" t="inlineStr"/>
+      <c r="H100" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L100" s="14" t="inlineStr"/>
-      <c r="M100" s="14" t="inlineStr"/>
+        <v>1.19</v>
+      </c>
+      <c r="L100" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-30079</t>
+        </is>
+      </c>
+      <c r="M100" s="14" t="inlineStr">
+        <is>
+          <t>00152632</t>
+        </is>
+      </c>
       <c r="N100" s="15" t="n">
         <v>0</v>
       </c>
@@ -7884,22 +7902,22 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7922,23 +7940,23 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>6.25</v>
+        <v>1.19</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
@@ -7954,12 +7972,12 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -7969,7 +7987,7 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -7992,27 +8010,27 @@
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>230</v>
+        <v>401</v>
       </c>
       <c r="O102" s="16" t="n">
         <v>0</v>
@@ -8024,12 +8042,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8039,7 +8057,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8052,20 +8070,20 @@
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr"/>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L103" s="11" t="inlineStr"/>
       <c r="M103" s="11" t="inlineStr"/>
@@ -8082,12 +8100,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8097,7 +8115,7 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8120,23 +8138,23 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>2</v>
+        <v>6.75</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
@@ -8152,12 +8170,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8167,7 +8185,7 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8180,31 +8198,39 @@
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L105" s="11" t="inlineStr"/>
-      <c r="M105" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O105" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8214,22 +8240,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8245,21 +8271,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H106" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H106" s="14" t="inlineStr"/>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L106" s="14" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -8276,22 +8298,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8299,7 +8321,7 @@
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
@@ -8309,34 +8331,34 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O107" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8346,12 +8368,12 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -8361,7 +8383,7 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
@@ -8374,39 +8396,31 @@
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M108" s="14" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>5.75</v>
+      </c>
+      <c r="L108" s="14" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
       <c r="N108" s="15" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O108" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="15" t="n">
@@ -8416,22 +8430,22 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8449,19 +8463,19 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="L109" s="11" t="inlineStr"/>
       <c r="M109" s="11" t="inlineStr"/>
@@ -8478,22 +8492,22 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8501,44 +8515,44 @@
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28003</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="15" t="n">
@@ -8548,22 +8562,22 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8576,7 +8590,7 @@
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
@@ -8586,21 +8600,29 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L111" s="11" t="inlineStr"/>
-      <c r="M111" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O111" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="12" t="n">
@@ -8610,22 +8632,22 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8638,7 +8660,7 @@
       </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H112" s="14" t="inlineStr">
@@ -8648,25 +8670,17 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L112" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M112" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L112" s="14" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
       <c r="N112" s="15" t="n">
         <v>0</v>
       </c>
@@ -8680,22 +8694,22 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8713,28 +8727,28 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-28003</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>412981</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
@@ -8750,12 +8764,12 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -8765,7 +8779,7 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8783,16 +8797,16 @@
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K114" s="14" t="n">
         <v>0.5</v>
@@ -8812,12 +8826,12 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -8827,13 +8841,11 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E115" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v/>
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
@@ -8842,7 +8854,7 @@
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
@@ -8852,17 +8864,25 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L115" s="11" t="inlineStr"/>
-      <c r="M115" s="11" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L115" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M115" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N115" s="12" t="n">
         <v>0</v>
       </c>
@@ -8876,24 +8896,26 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C116" s="14" t="inlineStr"/>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E116" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="n">
+        <v/>
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
@@ -8912,17 +8934,25 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L116" s="14" t="inlineStr"/>
-      <c r="M116" s="14" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L116" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M116" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N116" s="15" t="n">
         <v>0</v>
       </c>
@@ -8936,21 +8966,27 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C117" s="11" t="inlineStr"/>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="inlineStr"/>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v/>
+      </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -8958,17 +8994,21 @@
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H117" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K117" s="11" t="n">
         <v>0.5</v>
@@ -8986,31 +9026,271 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="17" t="inlineStr">
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F118" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G118" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H118" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I118" s="14" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J118" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K118" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" s="14" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+      <c r="N118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr"/>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J119" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K119" s="11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L119" s="11" t="inlineStr"/>
+      <c r="M119" s="11" t="inlineStr"/>
+      <c r="N119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-2155</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="inlineStr">
+        <is>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
+      <c r="F120" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G120" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H120" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I120" s="14" t="inlineStr">
+        <is>
+          <t>02/08/2023</t>
+        </is>
+      </c>
+      <c r="J120" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K120" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L120" s="14" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+      <c r="N120" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1326</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr"/>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr"/>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr"/>
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="J121" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L121" s="11" t="inlineStr"/>
+      <c r="M121" s="11" t="inlineStr"/>
+      <c r="N121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B118" s="17" t="inlineStr"/>
-      <c r="C118" s="17" t="inlineStr"/>
-      <c r="D118" s="17" t="inlineStr"/>
-      <c r="E118" s="17" t="inlineStr"/>
-      <c r="F118" s="17" t="inlineStr"/>
-      <c r="G118" s="17" t="inlineStr"/>
-      <c r="H118" s="17" t="inlineStr"/>
-      <c r="I118" s="17" t="inlineStr"/>
-      <c r="J118" s="17" t="inlineStr"/>
-      <c r="K118" s="17" t="inlineStr"/>
-      <c r="L118" s="17" t="inlineStr"/>
-      <c r="M118" s="17" t="inlineStr"/>
-      <c r="N118" s="18" t="n">
-        <v>66668.69399999999</v>
-      </c>
-      <c r="O118" s="18" t="n">
+      <c r="B122" s="17" t="inlineStr"/>
+      <c r="C122" s="17" t="inlineStr"/>
+      <c r="D122" s="17" t="inlineStr"/>
+      <c r="E122" s="17" t="inlineStr"/>
+      <c r="F122" s="17" t="inlineStr"/>
+      <c r="G122" s="17" t="inlineStr"/>
+      <c r="H122" s="17" t="inlineStr"/>
+      <c r="I122" s="17" t="inlineStr"/>
+      <c r="J122" s="17" t="inlineStr"/>
+      <c r="K122" s="17" t="inlineStr"/>
+      <c r="L122" s="17" t="inlineStr"/>
+      <c r="M122" s="17" t="inlineStr"/>
+      <c r="N122" s="18" t="n">
+        <v>62494.694</v>
+      </c>
+      <c r="O122" s="18" t="n">
         <v>4805.85</v>
       </c>
-      <c r="P118" s="18" t="n">
-        <v>36.54</v>
+      <c r="P122" s="18" t="n">
+        <v>31.99</v>
       </c>
     </row>
   </sheetData>
@@ -9129,6 +9409,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId117"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9703,26 +9987,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>99.5</v>
+        <v>112.75</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>5.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>127.25</v>
+        <v>141</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>39.75</v>
+        <v>52.75</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>601.65</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
     </row>
@@ -9733,7 +10017,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>4.25</v>
+        <v>9.25</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -9742,17 +10026,17 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>4.25</v>
+        <v>9.25</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>103.74</v>
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
@@ -9764,7 +10048,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>54</v>
+        <v>66.25</v>
       </c>
     </row>
   </sheetData>
@@ -9852,13 +10136,13 @@
         <v>386762</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>142839</v>
+        <v>146381</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>243923</v>
+        <v>240382</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>153202</v>
+        <v>149661</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21179</v>
@@ -9902,13 +10186,13 @@
         <v>212052</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>74592</v>
+        <v>78133</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>137460</v>
+        <v>133918</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>64570</v>
+        <v>61029</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>9871</v>
@@ -9928,7 +10212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -9952,7 +10236,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 6 commande(s)</t>
+          <t>Épics créées ce mois — 8 commande(s)</t>
         </is>
       </c>
     </row>
@@ -10007,22 +10291,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35008</t>
+          <t>PDMDEP-35088</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35000</t>
+          <t>PDMDEP-35082</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
+          <t>FREJUS</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -10032,7 +10316,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -10042,32 +10326,32 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00178436</t>
+          <t>00152501</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
-        <v>500</v>
+        <v>3541.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34961</t>
+          <t>PDMDEP-35008</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34953</t>
+          <t>PDMDEP-35000</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAIE-MAHAULT</t>
+          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -10087,37 +10371,37 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00178176</t>
+          <t>00178436</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>4050</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34993</t>
+          <t>PDMDEP-34961</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34989</t>
+          <t>PDMDEP-34953</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t>COMMUNE DE BAIE-MAHAULT</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
@@ -10132,32 +10416,32 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00178306</t>
+          <t>00178176</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>1500</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-35041</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -10177,27 +10461,27 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178778</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>2200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34970</t>
+          <t>PDMDEP-34993</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34966</t>
+          <t>PDMDEP-34989</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -10222,104 +10506,152 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00146508</t>
+          <t>00178306</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-34979</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34975</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>VILLE DE SURESNES</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>00178226</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34970</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34966</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Commune de Villeneuve D'Ascq</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>00146508</t>
+        </is>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-34929</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-34925</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>00178034</t>
         </is>
       </c>
-      <c r="I10" s="26" t="n">
+      <c r="I12" s="26" t="n">
         <v>2300</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="17" t="n"/>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>6 commande(s)</t>
-        </is>
-      </c>
-      <c r="I11" s="24" t="n">
-        <v>10550</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>dont Littéralis</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="17" t="n"/>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>4 commande(s)</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="n">
-        <v>6000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B13" s="17" t="n"/>
@@ -10330,11 +10662,53 @@
       <c r="G13" s="17" t="n"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>2 commande(s)</t>
+          <t>8 commande(s)</t>
         </is>
       </c>
       <c r="I13" s="24" t="n">
-        <v>4550</v>
+        <v>14092</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>dont Littéralis</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="17" t="n"/>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>5 commande(s)</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>3 commande(s)</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="n">
+        <v>8092</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-08-18.xlsx
+++ b/jira_export_2026-08-18.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>271 h</t>
+          <t>276 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P122"/>
+  <dimension ref="A1:P126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1982,12 +1982,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34337</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Commune de Chalons-sur-Saone</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Achat nouveau PAX A920</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2017,35 +2017,35 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34345</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00171711</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P18" s="15" t="n">
         <v>0</v>
@@ -2054,12 +2054,12 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
@@ -2105,19 +2105,19 @@
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34345</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00171711</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O19" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O19" s="12" t="n">
+        <v>50</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
@@ -2126,27 +2126,27 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
@@ -2177,16 +2177,16 @@
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>2127.2</v>
+        <v>769.5</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>0</v>
@@ -2198,32 +2198,32 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2270,32 +2270,32 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -2305,35 +2305,35 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O22" s="16" t="n">
-        <v>367.5</v>
+        <v>0</v>
       </c>
       <c r="P22" s="15" t="n">
         <v>0</v>
@@ -2342,12 +2342,12 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
@@ -2393,19 +2393,19 @@
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O23" s="16" t="n">
-        <v>0</v>
+        <v>367.5</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
@@ -2414,42 +2414,42 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34183</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MEGEVE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
@@ -2461,14 +2461,22 @@
         <v>2</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L24" s="14" t="inlineStr"/>
-      <c r="M24" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34201</t>
+        </is>
+      </c>
+      <c r="M24" s="14" t="inlineStr">
+        <is>
+          <t>00171162</t>
+        </is>
+      </c>
       <c r="N24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="15" t="n">
+        <v>1662</v>
+      </c>
+      <c r="O24" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="15" t="n">
@@ -2478,69 +2486,61 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34227</t>
-        </is>
-      </c>
-      <c r="M25" s="11" t="inlineStr">
-        <is>
-          <t>2026-0210095</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L25" s="11" t="inlineStr"/>
+      <c r="M25" s="11" t="inlineStr"/>
       <c r="N25" s="12" t="n">
-        <v>9623.1</v>
-      </c>
-      <c r="O25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P25" s="12" t="n">
@@ -2550,12 +2550,12 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
@@ -2601,16 +2601,16 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O26" s="16" t="n">
         <v>0</v>
@@ -2622,12 +2622,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2657,32 +2657,32 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2694,27 +2694,27 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
@@ -2745,16 +2745,16 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2766,32 +2766,32 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2801,32 +2801,32 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>9.75</v>
+        <v>0.25</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>242.9</v>
+        <v>510</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2838,27 +2838,27 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -2885,20 +2885,20 @@
         <v>2</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>220</v>
+        <v>242.9</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2910,32 +2910,32 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2945,34 +2945,34 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="O31" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="12" t="n">
@@ -2982,27 +2982,27 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3029,22 +3029,22 @@
         <v>2</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>680</v>
-      </c>
-      <c r="O32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="15" t="n">
@@ -3054,32 +3054,32 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Installation serveurs et montée de version TEST ET PROD</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3089,32 +3089,32 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>787.5</v>
+        <v>680</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3126,12 +3126,12 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3173,37 +3173,37 @@
         <v>2</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>8.75</v>
+        <v>0.75</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="15" t="n">
-        <v>416.29</v>
+        <v>787.5</v>
+      </c>
+      <c r="O34" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P34" s="15" t="n">
-        <v>47.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3245,52 +3245,52 @@
         <v>2</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O35" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O35" s="12" t="n">
+        <v>416.29</v>
       </c>
       <c r="P35" s="12" t="n">
-        <v>0</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -3310,27 +3310,27 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O36" s="16" t="n">
         <v>0</v>
@@ -3342,32 +3342,32 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33638</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOULINS</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier et MEP module Caisse</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -3377,34 +3377,34 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33647</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00169251</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="12" t="n">
+        <v>920</v>
+      </c>
+      <c r="O37" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="12" t="n">
@@ -3414,12 +3414,12 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33638</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DE MOULINS</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Migration GeODP Placier et MEP module Caisse</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -3454,29 +3454,29 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33647</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169251</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>4040</v>
-      </c>
-      <c r="O38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
@@ -3486,27 +3486,27 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
@@ -3533,20 +3533,20 @@
         <v>2</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1017.5</v>
+        <v>4040</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3558,27 +3558,27 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
@@ -3593,32 +3593,32 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K40" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>1416</v>
+        <v>1017.5</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3630,32 +3630,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>171.4</v>
+        <v>1416</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3702,32 +3702,32 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
@@ -3753,16 +3753,16 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>344</v>
+        <v>171.4</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3774,32 +3774,32 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3821,20 +3821,20 @@
         <v>3</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>514.2</v>
+        <v>344</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3846,32 +3846,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3886,27 +3886,27 @@
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>500</v>
+        <v>514.2</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3918,27 +3918,27 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
@@ -3969,16 +3969,16 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3990,32 +3990,32 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4025,32 +4025,32 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4113,18 +4113,18 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="12" t="n">
+        <v>625</v>
+      </c>
+      <c r="O47" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P47" s="12" t="n">
@@ -4134,32 +4134,32 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -4169,49 +4169,49 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>2</v>
+        <v>4.12</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4246,59 +4246,59 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O49" s="16" t="n">
-        <v>0</v>
+        <v>910</v>
+      </c>
+      <c r="O49" s="12" t="n">
+        <v>910</v>
       </c>
       <c r="P49" s="12" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4318,64 +4318,64 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="15" t="n">
-        <v>323.7</v>
+        <v>1207</v>
+      </c>
+      <c r="O50" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P50" s="15" t="n">
-        <v>1294.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4385,69 +4385,69 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="O51" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O51" s="12" t="n">
+        <v>323.7</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>0</v>
+        <v>1294.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
@@ -4469,20 +4469,20 @@
         <v>4</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4494,32 +4494,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4529,49 +4529,49 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>2.75</v>
+        <v>1</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>1294.224</v>
+        <v>400</v>
       </c>
       <c r="O53" s="16" t="n">
-        <v>219.36</v>
+        <v>0</v>
       </c>
       <c r="P53" s="12" t="n">
-        <v>79.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H54" s="14" t="inlineStr">
@@ -4606,36 +4606,44 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L54" s="14" t="inlineStr"/>
-      <c r="M54" s="14" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L54" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-32629</t>
+        </is>
+      </c>
+      <c r="M54" s="14" t="inlineStr">
+        <is>
+          <t>00163182</t>
+        </is>
+      </c>
       <c r="N54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="15" t="n">
-        <v>0</v>
+        <v>1294.224</v>
+      </c>
+      <c r="O54" s="16" t="n">
+        <v>219.36</v>
       </c>
       <c r="P54" s="15" t="n">
-        <v>0</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -4645,12 +4653,12 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4660,7 +4668,7 @@
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
@@ -4677,22 +4685,14 @@
         <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-32556</t>
-        </is>
-      </c>
-      <c r="M55" s="11" t="inlineStr">
-        <is>
-          <t>00162313</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L55" s="11" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr"/>
       <c r="N55" s="12" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
@@ -4702,32 +4702,32 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4737,32 +4737,32 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K56" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4774,27 +4774,27 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
@@ -4825,16 +4825,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4846,32 +4846,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4881,32 +4881,32 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O58" s="16" t="n">
         <v>0</v>
@@ -4918,28 +4918,32 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C59" s="11" t="inlineStr"/>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4949,32 +4953,32 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>255</v>
+        <v>910</v>
       </c>
       <c r="O59" s="16" t="n">
         <v>0</v>
@@ -4986,27 +4990,23 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr"/>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5033,52 +5033,52 @@
         <v>5</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="15" t="n">
-        <v>100</v>
+        <v>255</v>
+      </c>
+      <c r="O60" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5093,49 +5093,49 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="O61" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O61" s="12" t="n">
+        <v>100</v>
       </c>
       <c r="P61" s="12" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
@@ -5181,16 +5181,16 @@
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>1000</v>
+        <v>590.15</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5202,32 +5202,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5237,34 +5237,34 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O63" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
@@ -5274,32 +5274,32 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -5309,34 +5309,34 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>285</v>
-      </c>
-      <c r="O64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
@@ -5346,32 +5346,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
@@ -5397,16 +5397,16 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O65" s="16" t="n">
         <v>0</v>
@@ -5418,12 +5418,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
@@ -5469,16 +5469,16 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5490,32 +5490,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -5541,16 +5541,16 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5562,27 +5562,27 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5597,32 +5597,32 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K68" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5634,12 +5634,12 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
@@ -5685,16 +5685,16 @@
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5706,32 +5706,32 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -5741,32 +5741,32 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5778,12 +5778,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
@@ -5825,14 +5825,22 @@
         <v>6</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L71" s="11" t="inlineStr"/>
-      <c r="M71" s="11" t="inlineStr"/>
+        <v>11.75</v>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12" t="n">
+        <v>700</v>
+      </c>
+      <c r="O71" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -5842,27 +5850,27 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5872,7 +5880,7 @@
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H72" s="14" t="inlineStr">
@@ -5882,29 +5890,21 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L72" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M72" s="14" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L72" s="14" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
       <c r="N72" s="15" t="n">
-        <v>416.475</v>
-      </c>
-      <c r="O72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
@@ -5914,32 +5914,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5949,32 +5949,32 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>210</v>
+        <v>416.475</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -5986,12 +5986,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6037,16 +6037,16 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>281</v>
+        <v>210</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6058,12 +6058,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6109,16 +6109,16 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6130,12 +6130,12 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
@@ -6181,16 +6181,16 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6202,12 +6202,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6242,29 +6242,29 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="12" t="n">
+        <v>255</v>
+      </c>
+      <c r="O77" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P77" s="12" t="n">
@@ -6274,12 +6274,12 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -6289,12 +6289,12 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6314,29 +6314,29 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>140</v>
-      </c>
-      <c r="O78" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
@@ -6346,32 +6346,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6381,32 +6381,32 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O79" s="16" t="n">
         <v>0</v>
@@ -6418,27 +6418,27 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -6458,29 +6458,29 @@
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="15" t="n">
+        <v>690</v>
+      </c>
+      <c r="O80" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
@@ -6541,18 +6541,18 @@
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O81" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -6613,16 +6613,16 @@
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O82" s="16" t="n">
         <v>0</v>
@@ -6634,32 +6634,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6669,32 +6669,32 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>725</v>
+        <v>787.5</v>
       </c>
       <c r="O83" s="16" t="n">
         <v>0</v>
@@ -6706,30 +6706,32 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E84" s="14" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -6739,34 +6741,34 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="15" t="n">
+        <v>725</v>
+      </c>
+      <c r="O84" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="15" t="n">
@@ -6776,12 +6778,12 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -6791,13 +6793,11 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v/>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
@@ -6816,23 +6816,23 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
@@ -7115,18 +7115,18 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O89" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -7136,12 +7136,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7151,11 +7151,13 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E90" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
@@ -7174,29 +7176,29 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O90" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
@@ -7206,12 +7208,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7221,7 +7223,7 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -7239,34 +7241,34 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O91" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="12" t="n">
@@ -7276,28 +7278,26 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E92" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="n">
+        <v/>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
@@ -7316,23 +7316,23 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0.25</v>
+        <v>6</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
@@ -7348,12 +7348,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7363,13 +7363,11 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>Script purge de données</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v/>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
@@ -7378,31 +7376,39 @@
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L93" s="11" t="inlineStr"/>
-      <c r="M93" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L93" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27017</t>
+        </is>
+      </c>
+      <c r="M93" s="11" t="inlineStr">
+        <is>
+          <t>00141205</t>
+        </is>
+      </c>
       <c r="N93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="12" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O93" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -7412,12 +7418,12 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
@@ -7427,11 +7433,13 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -7450,23 +7458,23 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
@@ -7482,26 +7490,28 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E95" s="11" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
@@ -7510,17 +7520,17 @@
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
@@ -7529,16 +7539,8 @@
       <c r="K95" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L95" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27995</t>
-        </is>
-      </c>
-      <c r="M95" s="11" t="inlineStr">
-        <is>
-          <t>501218</t>
-        </is>
-      </c>
+      <c r="L95" s="11" t="inlineStr"/>
+      <c r="M95" s="11" t="inlineStr"/>
       <c r="N95" s="12" t="n">
         <v>0</v>
       </c>
@@ -7552,22 +7554,22 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7590,23 +7592,23 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
@@ -7622,22 +7624,22 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7660,23 +7662,23 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
@@ -7692,12 +7694,12 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
@@ -7707,7 +7709,7 @@
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
@@ -7730,23 +7732,23 @@
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
@@ -7762,12 +7764,12 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7777,7 +7779,7 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7800,23 +7802,23 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
         <v>13</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>1.19</v>
+        <v>0.25</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
@@ -7847,7 +7849,7 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
@@ -7881,12 +7883,12 @@
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
@@ -7951,12 +7953,12 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
@@ -7972,22 +7974,22 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -8005,34 +8007,34 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0.5</v>
+        <v>1.19</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O102" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
@@ -8042,12 +8044,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8057,7 +8059,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8073,20 +8075,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H103" s="11" t="inlineStr"/>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L103" s="11" t="inlineStr"/>
-      <c r="M103" s="11" t="inlineStr"/>
+        <v>1.19</v>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27365</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>491593</t>
+        </is>
+      </c>
       <c r="N103" s="12" t="n">
         <v>0</v>
       </c>
@@ -8100,12 +8114,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8115,7 +8129,7 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8133,34 +8147,34 @@
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>6.75</v>
+        <v>0.5</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O104" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8170,22 +8184,22 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8201,36 +8215,24 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H105" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H105" s="11" t="inlineStr"/>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
         <v>16</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28034</t>
-        </is>
-      </c>
-      <c r="M105" s="11" t="inlineStr">
-        <is>
-          <t>475575</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L105" s="11" t="inlineStr"/>
+      <c r="M105" s="11" t="inlineStr"/>
       <c r="N105" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O105" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8240,22 +8242,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8268,23 +8270,35 @@
       </c>
       <c r="G106" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H106" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H106" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L106" s="14" t="inlineStr"/>
-      <c r="M106" s="14" t="inlineStr"/>
+        <v>6.75</v>
+      </c>
+      <c r="L106" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M106" s="14" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
       <c r="N106" s="15" t="n">
         <v>0</v>
       </c>
@@ -8298,12 +8312,12 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
@@ -8313,7 +8327,7 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8331,34 +8345,34 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O107" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8368,22 +8382,22 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
@@ -8399,21 +8413,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H108" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H108" s="14" t="inlineStr"/>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>5.75</v>
+        <v>1.25</v>
       </c>
       <c r="L108" s="14" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -8430,12 +8440,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8445,7 +8455,7 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8458,7 +8468,7 @@
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
@@ -8468,17 +8478,25 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L109" s="11" t="inlineStr"/>
-      <c r="M109" s="11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L109" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M109" s="11" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N109" s="12" t="n">
         <v>0</v>
       </c>
@@ -8492,22 +8510,22 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8515,44 +8533,36 @@
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M110" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>5.75</v>
+      </c>
+      <c r="L110" s="14" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
       <c r="N110" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O110" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="15" t="n">
@@ -8562,12 +8572,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8577,7 +8587,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8590,39 +8600,31 @@
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M111" s="11" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L111" s="11" t="inlineStr"/>
+      <c r="M111" s="11" t="inlineStr"/>
       <c r="N111" s="12" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O111" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="12" t="n">
@@ -8632,22 +8634,22 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8655,36 +8657,44 @@
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L112" s="14" t="inlineStr"/>
-      <c r="M112" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L112" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M112" s="14" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N112" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O112" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="15" t="n">
@@ -8694,12 +8704,12 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
@@ -8709,7 +8719,7 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8722,7 +8732,7 @@
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
@@ -8732,29 +8742,29 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28003</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O113" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8764,12 +8774,12 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -8779,7 +8789,7 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8802,14 +8812,14 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L114" s="14" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -8826,12 +8836,12 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -8841,7 +8851,7 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8854,7 +8864,7 @@
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
@@ -8864,23 +8874,23 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-28003</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>412981</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
@@ -8896,12 +8906,12 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -8911,7 +8921,7 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -8929,30 +8939,22 @@
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L116" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M116" s="14" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L116" s="14" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
       <c r="N116" s="15" t="n">
         <v>0</v>
       </c>
@@ -8966,22 +8968,22 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -8999,16 +9001,16 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K117" s="11" t="n">
         <v>0.5</v>
@@ -9028,12 +9030,12 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
@@ -9043,13 +9045,11 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E118" s="14" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="n">
+        <v/>
       </c>
       <c r="F118" s="14" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H118" s="14" t="inlineStr">
@@ -9068,17 +9068,25 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="14" t="inlineStr"/>
-      <c r="M118" s="14" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L118" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M118" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N118" s="15" t="n">
         <v>0</v>
       </c>
@@ -9092,24 +9100,26 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C119" s="11" t="inlineStr"/>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v/>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
@@ -9128,17 +9138,25 @@
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L119" s="11" t="inlineStr"/>
-      <c r="M119" s="11" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L119" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M119" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N119" s="12" t="n">
         <v>0</v>
       </c>
@@ -9152,12 +9170,12 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -9167,13 +9185,11 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
-        </is>
-      </c>
-      <c r="E120" s="14" t="inlineStr">
-        <is>
-          <t>Montée de version + Pastell</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="n">
+        <v/>
       </c>
       <c r="F120" s="14" t="inlineStr">
         <is>
@@ -9187,16 +9203,16 @@
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K120" s="14" t="n">
         <v>0.5</v>
@@ -9216,21 +9232,29 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C121" s="11" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="inlineStr"/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9238,20 +9262,24 @@
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H121" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K121" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="K121" s="11" t="n">
-        <v>0.5</v>
       </c>
       <c r="L121" s="11" t="inlineStr"/>
       <c r="M121" s="11" t="inlineStr"/>
@@ -9266,31 +9294,259 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="17" t="inlineStr">
+      <c r="A122" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr"/>
+      <c r="D122" s="14" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F122" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G122" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H122" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I122" s="14" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J122" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K122" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L122" s="14" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+      <c r="N122" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-2155</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I123" s="11" t="inlineStr">
+        <is>
+          <t>02/08/2023</t>
+        </is>
+      </c>
+      <c r="J123" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K123" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr"/>
+      <c r="M123" s="11" t="inlineStr"/>
+      <c r="N123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1326</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="inlineStr"/>
+      <c r="D124" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr"/>
+      <c r="F124" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G124" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H124" s="14" t="inlineStr"/>
+      <c r="I124" s="14" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="J124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L124" s="14" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+      <c r="N124" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1320</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr"/>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr"/>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr"/>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="J125" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L125" s="11" t="inlineStr"/>
+      <c r="M125" s="11" t="inlineStr"/>
+      <c r="N125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B122" s="17" t="inlineStr"/>
-      <c r="C122" s="17" t="inlineStr"/>
-      <c r="D122" s="17" t="inlineStr"/>
-      <c r="E122" s="17" t="inlineStr"/>
-      <c r="F122" s="17" t="inlineStr"/>
-      <c r="G122" s="17" t="inlineStr"/>
-      <c r="H122" s="17" t="inlineStr"/>
-      <c r="I122" s="17" t="inlineStr"/>
-      <c r="J122" s="17" t="inlineStr"/>
-      <c r="K122" s="17" t="inlineStr"/>
-      <c r="L122" s="17" t="inlineStr"/>
-      <c r="M122" s="17" t="inlineStr"/>
-      <c r="N122" s="18" t="n">
+      <c r="B126" s="17" t="inlineStr"/>
+      <c r="C126" s="17" t="inlineStr"/>
+      <c r="D126" s="17" t="inlineStr"/>
+      <c r="E126" s="17" t="inlineStr"/>
+      <c r="F126" s="17" t="inlineStr"/>
+      <c r="G126" s="17" t="inlineStr"/>
+      <c r="H126" s="17" t="inlineStr"/>
+      <c r="I126" s="17" t="inlineStr"/>
+      <c r="J126" s="17" t="inlineStr"/>
+      <c r="K126" s="17" t="inlineStr"/>
+      <c r="L126" s="17" t="inlineStr"/>
+      <c r="M126" s="17" t="inlineStr"/>
+      <c r="N126" s="18" t="n">
         <v>62494.694</v>
       </c>
-      <c r="O122" s="18" t="n">
-        <v>4805.85</v>
-      </c>
-      <c r="P122" s="18" t="n">
-        <v>31.99</v>
+      <c r="O126" s="18" t="n">
+        <v>4805.849999999999</v>
+      </c>
+      <c r="P126" s="18" t="n">
+        <v>31.21</v>
       </c>
     </row>
   </sheetData>
@@ -9413,6 +9669,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9987,16 +10247,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>112.75</v>
+        <v>115.5</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>141</v>
+        <v>144.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>52.75</v>
@@ -10006,7 +10266,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>24.0%</t>
         </is>
       </c>
     </row>
@@ -10017,7 +10277,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -10026,7 +10286,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0.5</v>
@@ -10036,7 +10296,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10308,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>66.25</v>
+        <v>67.25</v>
       </c>
     </row>
   </sheetData>
@@ -10133,10 +10393,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>386762</v>
+        <v>387747</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>146381</v>
+        <v>147366</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>240382</v>
@@ -10183,10 +10443,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>212052</v>
+        <v>213037</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>78133</v>
+        <v>79118</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>133918</v>
@@ -10212,7 +10472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -10236,7 +10496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 8 commande(s)</t>
+          <t>Épics créées ce mois — 9 commande(s)</t>
         </is>
       </c>
     </row>
@@ -10291,12 +10551,12 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35088</t>
+          <t>PDMDEP-35114</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35082</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -10306,7 +10566,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>FREJUS</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -10326,32 +10586,32 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00152501</t>
+          <t>00178806</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
-        <v>3541.5</v>
+        <v>985</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35008</t>
+          <t>PDMDEP-35088</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35000</t>
+          <t>PDMDEP-35082</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
+          <t>FREJUS</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -10361,7 +10621,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -10371,32 +10631,32 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00178436</t>
+          <t>00152501</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>500</v>
+        <v>3541.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34961</t>
+          <t>PDMDEP-35008</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34953</t>
+          <t>PDMDEP-35000</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAIE-MAHAULT</t>
+          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -10416,37 +10676,37 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00178176</t>
+          <t>00178436</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>4050</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35041</t>
+          <t>PDMDEP-34961</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-34953</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>COMMUNE DE BAIE-MAHAULT</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -10461,32 +10721,32 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00178778</t>
+          <t>00178176</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>0</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34993</t>
+          <t>PDMDEP-35041</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34989</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -10506,32 +10766,32 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00178306</t>
+          <t>00178778</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-34993</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-34989</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -10551,22 +10811,22 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178306</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34970</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34966</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -10576,7 +10836,7 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -10596,83 +10856,107 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00146508</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-34970</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34966</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Commune de Villeneuve D'Ascq</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>00146508</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-34929</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-34925</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>00178034</t>
         </is>
       </c>
-      <c r="I12" s="26" t="n">
+      <c r="I13" s="25" t="n">
         <v>2300</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="17" t="n"/>
-      <c r="E13" s="17" t="n"/>
-      <c r="F13" s="17" t="n"/>
-      <c r="G13" s="17" t="n"/>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>8 commande(s)</t>
-        </is>
-      </c>
-      <c r="I13" s="24" t="n">
-        <v>14092</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B14" s="17" t="n"/>
@@ -10683,17 +10967,17 @@
       <c r="G14" s="17" t="n"/>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>5 commande(s)</t>
+          <t>9 commande(s)</t>
         </is>
       </c>
       <c r="I14" s="24" t="n">
-        <v>6000</v>
+        <v>15076</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B15" s="17" t="n"/>
@@ -10704,11 +10988,32 @@
       <c r="G15" s="17" t="n"/>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>3 commande(s)</t>
+          <t>5 commande(s)</t>
         </is>
       </c>
       <c r="I15" s="24" t="n">
-        <v>8092</v>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>4 commande(s)</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>9076</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-08-18.xlsx
+++ b/jira_export_2026-08-18.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>276 h</t>
+          <t>284 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>262</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P126"/>
+  <dimension ref="A1:P127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1270,27 +1270,27 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34925</t>
+          <t>PDMDEP-34966</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
+          <t>[Commune de Villeneuve D'Ascq] - Ajout de 5 licences supplémentaires Littéralis</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
+          <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>AME multi-communes acheté par la CC</t>
+          <t>Ajout de 5 licences supplémentaires Littéralis</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -1310,23 +1310,23 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J8" s="14" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34929</t>
+          <t>PDMDEP-34970</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>00178034</t>
+          <t>00146508</t>
         </is>
       </c>
       <c r="N8" s="15" t="n">
@@ -1342,27 +1342,27 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34857</t>
+          <t>PDMDEP-34925</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Matching DA/DPA</t>
+          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Matching DA/DPA</t>
+          <t>AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -1382,23 +1382,23 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="11" t="n">
-        <v>0.25</v>
-      </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34861</t>
+          <t>PDMDEP-34929</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>00177271</t>
+          <t>00178034</t>
         </is>
       </c>
       <c r="N9" s="12" t="n">
@@ -1414,27 +1414,27 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34848</t>
+          <t>PDMDEP-34857</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
+          <t>[COMMUNE DE BIARRITZ] - Matching DA/DPA</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Marine MASINGARBE</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
+          <t>Matching DA/DPA</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -1454,17 +1454,25 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J10" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L10" s="14" t="inlineStr"/>
-      <c r="M10" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34861</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="inlineStr">
+        <is>
+          <t>00177271</t>
+        </is>
+      </c>
       <c r="N10" s="15" t="n">
         <v>0</v>
       </c>
@@ -1478,42 +1486,42 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34848</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
+          <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Marine MASINGARBE</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -1525,23 +1533,15 @@
         <v>1</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34825</t>
-        </is>
-      </c>
-      <c r="M11" s="11" t="inlineStr">
-        <is>
-          <t>00177218</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L11" s="11" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr"/>
       <c r="N11" s="12" t="n">
-        <v>2419</v>
+        <v>0</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>2419</v>
+        <v>0</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
@@ -1550,27 +1550,27 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
@@ -1597,23 +1597,23 @@
         <v>1</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="N12" s="15" t="n">
-        <v>429.3</v>
-      </c>
-      <c r="O12" s="16" t="n">
-        <v>0</v>
+        <v>2419</v>
+      </c>
+      <c r="O12" s="15" t="n">
+        <v>2419</v>
       </c>
       <c r="P12" s="15" t="n">
         <v>0</v>
@@ -1622,12 +1622,12 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34694</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Commune du Tampon</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1657,32 +1657,32 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34701</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00176675</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>789.5</v>
+        <v>429.3</v>
       </c>
       <c r="O13" s="16" t="n">
         <v>0</v>
@@ -1694,32 +1694,32 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
@@ -1745,16 +1745,16 @@
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
-        <v>495</v>
+        <v>789.5</v>
       </c>
       <c r="O14" s="16" t="n">
         <v>0</v>
@@ -1766,32 +1766,32 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34521</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE FRONTON] - Simple commande de Pax pour installer Placier dessus</t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE FRONTON</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Simple commande de Pax pour installer Placier dessus</t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -1806,29 +1806,29 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34527</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00173007</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="12" t="n">
+        <v>495</v>
+      </c>
+      <c r="O15" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="12" t="n">
@@ -1838,32 +1838,32 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34521</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[COMMUNE DE FRONTON] - Simple commande de Pax pour installer Placier dessus</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>COMMUNE DE FRONTON</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t>Simple commande de Pax pour installer Placier dessus</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1878,29 +1878,29 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34527</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00173007</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>1892</v>
-      </c>
-      <c r="O16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="15" t="n">
@@ -1910,32 +1910,32 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[Commune de La Flèche] - Migration GEODP Placier et ODP</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -1945,32 +1945,32 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>895</v>
+        <v>1892</v>
       </c>
       <c r="O17" s="16" t="n">
         <v>0</v>
@@ -1982,27 +1982,27 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE LA FLÈCHE] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2022,29 +2022,29 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="15" t="n">
+        <v>895</v>
+      </c>
+      <c r="O18" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P18" s="15" t="n">
@@ -2054,12 +2054,12 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34337</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Commune de Chalons-sur-Saone</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Achat nouveau PAX A920</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2089,35 +2089,35 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34345</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00171711</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
@@ -2126,12 +2126,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
@@ -2177,19 +2177,19 @@
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34345</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00171711</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O20" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O20" s="15" t="n">
+        <v>50</v>
       </c>
       <c r="P20" s="15" t="n">
         <v>0</v>
@@ -2198,27 +2198,27 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
@@ -2249,16 +2249,16 @@
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>2127.2</v>
+        <v>769.5</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2270,32 +2270,32 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -2305,32 +2305,32 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>10.25</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O22" s="16" t="n">
         <v>0</v>
@@ -2342,32 +2342,32 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2377,35 +2377,35 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O23" s="16" t="n">
-        <v>367.5</v>
+        <v>0</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
@@ -2414,12 +2414,12 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
@@ -2465,19 +2465,19 @@
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O24" s="16" t="n">
-        <v>0</v>
+        <v>367.5</v>
       </c>
       <c r="P24" s="15" t="n">
         <v>0</v>
@@ -2486,42 +2486,42 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34183</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MEGEVE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
@@ -2533,14 +2533,22 @@
         <v>2</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L25" s="11" t="inlineStr"/>
-      <c r="M25" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34201</t>
+        </is>
+      </c>
+      <c r="M25" s="11" t="inlineStr">
+        <is>
+          <t>00171162</t>
+        </is>
+      </c>
       <c r="N25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="12" t="n">
+        <v>1662</v>
+      </c>
+      <c r="O25" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P25" s="12" t="n">
@@ -2550,69 +2558,61 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34227</t>
-        </is>
-      </c>
-      <c r="M26" s="14" t="inlineStr">
-        <is>
-          <t>2026-0210095</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L26" s="14" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
       <c r="N26" s="15" t="n">
-        <v>9623.1</v>
-      </c>
-      <c r="O26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="15" t="n">
@@ -2622,12 +2622,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
@@ -2673,16 +2673,16 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2694,12 +2694,12 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2729,32 +2729,32 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2766,27 +2766,27 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
@@ -2817,16 +2817,16 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2838,32 +2838,32 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2873,32 +2873,32 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>9.75</v>
+        <v>0.25</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>242.9</v>
+        <v>510</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2910,27 +2910,27 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2957,20 +2957,20 @@
         <v>2</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>220</v>
+        <v>242.9</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2982,32 +2982,32 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -3017,34 +3017,34 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="15" t="n">
+        <v>220</v>
+      </c>
+      <c r="O32" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="15" t="n">
@@ -3054,27 +3054,27 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3101,22 +3101,22 @@
         <v>2</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>680</v>
-      </c>
-      <c r="O33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="12" t="n">
@@ -3126,32 +3126,32 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Installation serveurs et montée de version TEST ET PROD</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>787.5</v>
+        <v>680</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3198,12 +3198,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3245,37 +3245,37 @@
         <v>2</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>8.75</v>
+        <v>0.75</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="12" t="n">
-        <v>416.29</v>
+        <v>787.5</v>
+      </c>
+      <c r="O35" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P35" s="12" t="n">
-        <v>47.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -3317,52 +3317,52 @@
         <v>2</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O36" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O36" s="15" t="n">
+        <v>416.29</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>0</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3382,27 +3382,27 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O37" s="16" t="n">
         <v>0</v>
@@ -3414,32 +3414,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33638</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOULINS</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier et MEP module Caisse</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3449,34 +3449,34 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33647</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00169251</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="15" t="n">
+        <v>920</v>
+      </c>
+      <c r="O38" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
@@ -3486,12 +3486,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33638</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DE MOULINS</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Migration GeODP Placier et MEP module Caisse</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3526,29 +3526,29 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33647</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169251</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>4040</v>
-      </c>
-      <c r="O39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="12" t="n">
@@ -3558,27 +3558,27 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
@@ -3605,20 +3605,20 @@
         <v>2</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>1017.5</v>
+        <v>4040</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3630,27 +3630,27 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3665,32 +3665,32 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K41" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>1416</v>
+        <v>1017.5</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3702,32 +3702,32 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
@@ -3753,16 +3753,16 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>171.4</v>
+        <v>1416</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3774,32 +3774,32 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3825,16 +3825,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>344</v>
+        <v>171.4</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3846,32 +3846,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3893,20 +3893,20 @@
         <v>3</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>514.2</v>
+        <v>344</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3918,32 +3918,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3958,27 +3958,27 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>500</v>
+        <v>514.2</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3990,27 +3990,27 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
@@ -4041,16 +4041,16 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4062,32 +4062,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
         <v>3</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>4.12</v>
+        <v>4.38</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="15" t="n">
+        <v>625</v>
+      </c>
+      <c r="O48" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P48" s="15" t="n">
@@ -4206,32 +4206,32 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4241,49 +4241,49 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>2</v>
+        <v>4.38</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="P49" s="12" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4318,59 +4318,59 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O50" s="16" t="n">
-        <v>0</v>
+        <v>910</v>
+      </c>
+      <c r="O50" s="15" t="n">
+        <v>910</v>
       </c>
       <c r="P50" s="15" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4390,64 +4390,64 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="12" t="n">
-        <v>323.7</v>
+        <v>1207</v>
+      </c>
+      <c r="O51" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>1294.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4457,69 +4457,69 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="O52" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O52" s="15" t="n">
+        <v>323.7</v>
       </c>
       <c r="P52" s="15" t="n">
-        <v>0</v>
+        <v>1294.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
@@ -4541,20 +4541,20 @@
         <v>4</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4566,32 +4566,32 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4601,49 +4601,49 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>2.75</v>
+        <v>1</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>1294.224</v>
+        <v>400</v>
       </c>
       <c r="O54" s="16" t="n">
-        <v>219.36</v>
+        <v>0</v>
       </c>
       <c r="P54" s="15" t="n">
-        <v>79.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
@@ -4678,36 +4678,44 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L55" s="11" t="inlineStr"/>
-      <c r="M55" s="11" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L55" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32629</t>
+        </is>
+      </c>
+      <c r="M55" s="11" t="inlineStr">
+        <is>
+          <t>00163182</t>
+        </is>
+      </c>
       <c r="N55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="12" t="n">
-        <v>0</v>
+        <v>1294.224</v>
+      </c>
+      <c r="O55" s="16" t="n">
+        <v>219.36</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>0</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -4717,12 +4725,12 @@
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4732,7 +4740,7 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H56" s="14" t="inlineStr">
@@ -4749,22 +4757,14 @@
         <v>4</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-32556</t>
-        </is>
-      </c>
-      <c r="M56" s="14" t="inlineStr">
-        <is>
-          <t>00162313</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L56" s="14" t="inlineStr"/>
+      <c r="M56" s="14" t="inlineStr"/>
       <c r="N56" s="15" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="15" t="n">
@@ -4774,32 +4774,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4809,32 +4809,32 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K57" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4846,27 +4846,27 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
@@ -4897,16 +4897,16 @@
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O58" s="16" t="n">
         <v>0</v>
@@ -4918,32 +4918,32 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4953,32 +4953,32 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O59" s="16" t="n">
         <v>0</v>
@@ -4990,28 +4990,32 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="inlineStr"/>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5021,32 +5025,32 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>255</v>
+        <v>910</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5058,27 +5062,23 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
-        </is>
-      </c>
-      <c r="C61" s="11" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr"/>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5105,52 +5105,52 @@
         <v>5</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="n">
-        <v>100</v>
+        <v>255</v>
+      </c>
+      <c r="O61" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5165,49 +5165,49 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="O62" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O62" s="15" t="n">
+        <v>100</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
@@ -5253,16 +5253,16 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>1000</v>
+        <v>590.15</v>
       </c>
       <c r="O63" s="16" t="n">
         <v>0</v>
@@ -5274,32 +5274,32 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -5309,34 +5309,34 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O64" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
@@ -5346,32 +5346,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5381,34 +5381,34 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="O65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
@@ -5418,32 +5418,32 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
@@ -5469,16 +5469,16 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5490,12 +5490,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
@@ -5541,16 +5541,16 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5562,32 +5562,32 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
@@ -5613,16 +5613,16 @@
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5634,27 +5634,27 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5669,32 +5669,32 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K69" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5706,12 +5706,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5721,12 +5721,12 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
@@ -5757,16 +5757,16 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5778,32 +5778,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5813,32 +5813,32 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O71" s="16" t="n">
         <v>0</v>
@@ -5850,12 +5850,12 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H72" s="14" t="inlineStr">
@@ -5897,14 +5897,22 @@
         <v>6</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L72" s="14" t="inlineStr"/>
-      <c r="M72" s="14" t="inlineStr"/>
+        <v>12.25</v>
+      </c>
+      <c r="L72" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M72" s="14" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="O72" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
@@ -5914,27 +5922,27 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5944,7 +5952,7 @@
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
@@ -5954,29 +5962,21 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L73" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M73" s="11" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L73" s="11" t="inlineStr"/>
+      <c r="M73" s="11" t="inlineStr"/>
       <c r="N73" s="12" t="n">
-        <v>416.475</v>
-      </c>
-      <c r="O73" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -5986,32 +5986,32 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>210</v>
+        <v>416.475</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6058,12 +6058,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6109,16 +6109,16 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>281</v>
+        <v>210</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6130,12 +6130,12 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
@@ -6181,16 +6181,16 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6202,12 +6202,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
@@ -6253,16 +6253,16 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O77" s="16" t="n">
         <v>0</v>
@@ -6274,12 +6274,12 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -6289,12 +6289,12 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6314,29 +6314,29 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="15" t="n">
+        <v>255</v>
+      </c>
+      <c r="O78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
@@ -6346,12 +6346,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6386,29 +6386,29 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>140</v>
-      </c>
-      <c r="O79" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
@@ -6418,32 +6418,32 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O80" s="16" t="n">
         <v>0</v>
@@ -6490,27 +6490,27 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="12" t="n">
+        <v>690</v>
+      </c>
+      <c r="O81" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -6609,22 +6609,22 @@
         <v>7</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O82" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
@@ -6681,20 +6681,20 @@
         <v>7</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O83" s="16" t="n">
         <v>0</v>
@@ -6706,32 +6706,32 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -6741,32 +6741,32 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>725</v>
+        <v>787.5</v>
       </c>
       <c r="O84" s="16" t="n">
         <v>0</v>
@@ -6778,30 +6778,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6811,34 +6813,34 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="O85" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6848,12 +6850,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -6863,13 +6865,11 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E86" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="n">
+        <v/>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -6888,23 +6888,23 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
@@ -7187,18 +7187,18 @@
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O90" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
@@ -7208,12 +7208,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7223,11 +7223,13 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
@@ -7241,34 +7243,34 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O91" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="12" t="n">
@@ -7278,12 +7280,12 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
@@ -7293,7 +7295,7 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
@@ -7311,28 +7313,28 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>6</v>
+        <v>1.25</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
@@ -7348,12 +7350,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7363,7 +7365,7 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -7386,29 +7388,29 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O93" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -7418,28 +7420,26 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v/>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -7458,29 +7458,29 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
@@ -7490,27 +7490,27 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Script purge de données</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -7520,27 +7520,35 @@
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L95" s="11" t="inlineStr"/>
-      <c r="M95" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L95" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27578</t>
+        </is>
+      </c>
+      <c r="M95" s="11" t="inlineStr">
+        <is>
+          <t>499043</t>
+        </is>
+      </c>
       <c r="N95" s="12" t="n">
         <v>0</v>
       </c>
@@ -7554,26 +7562,28 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E96" s="14" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -7582,17 +7592,17 @@
       </c>
       <c r="G96" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
@@ -7601,16 +7611,8 @@
       <c r="K96" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="L96" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M96" s="14" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+      <c r="L96" s="14" t="inlineStr"/>
+      <c r="M96" s="14" t="inlineStr"/>
       <c r="N96" s="15" t="n">
         <v>0</v>
       </c>
@@ -7673,12 +7675,12 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
@@ -7694,22 +7696,22 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
@@ -7732,23 +7734,23 @@
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
@@ -7764,12 +7766,12 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7779,7 +7781,7 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7802,23 +7804,23 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
@@ -7834,12 +7836,12 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -7849,7 +7851,7 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
@@ -7872,23 +7874,23 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
         <v>13</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>1.19</v>
+        <v>0.25</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
@@ -7953,12 +7955,12 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
@@ -7989,7 +7991,7 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -8023,12 +8025,12 @@
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
@@ -8059,7 +8061,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8093,12 +8095,12 @@
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
@@ -8114,22 +8116,22 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8147,34 +8149,34 @@
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>0.5</v>
+        <v>1.19</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O104" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8184,22 +8186,22 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8215,24 +8217,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H105" s="11" t="inlineStr"/>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K105" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L105" s="11" t="inlineStr"/>
-      <c r="M105" s="11" t="inlineStr"/>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O105" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8242,22 +8256,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8273,11 +8287,7 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H106" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H106" s="14" t="inlineStr"/>
       <c r="I106" s="14" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -8287,18 +8297,10 @@
         <v>16</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="L106" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M106" s="14" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L106" s="14" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
       <c r="N106" s="15" t="n">
         <v>0</v>
       </c>
@@ -8312,12 +8314,12 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
@@ -8327,7 +8329,7 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8345,34 +8347,34 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
         <v>16</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O107" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8382,22 +8384,22 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
@@ -8410,27 +8412,39 @@
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H108" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H108" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L108" s="14" t="inlineStr"/>
-      <c r="M108" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L108" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M108" s="14" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N108" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O108" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="15" t="n">
@@ -8440,22 +8454,22 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8468,35 +8482,23 @@
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H109" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H109" s="11" t="inlineStr"/>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L109" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M109" s="11" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L109" s="11" t="inlineStr"/>
+      <c r="M109" s="11" t="inlineStr"/>
       <c r="N109" s="12" t="n">
         <v>0</v>
       </c>
@@ -8510,12 +8512,12 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
@@ -8525,7 +8527,7 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8538,7 +8540,7 @@
       </c>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H110" s="14" t="inlineStr">
@@ -8548,17 +8550,25 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L110" s="14" t="inlineStr"/>
-      <c r="M110" s="14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L110" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M110" s="14" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N110" s="15" t="n">
         <v>0</v>
       </c>
@@ -8572,12 +8582,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8587,7 +8597,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8610,14 +8620,14 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="L111" s="11" t="inlineStr"/>
       <c r="M111" s="11" t="inlineStr"/>
@@ -8634,22 +8644,22 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8657,44 +8667,36 @@
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M112" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L112" s="14" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
       <c r="N112" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O112" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="15" t="n">
@@ -8704,22 +8706,22 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8727,7 +8729,7 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
@@ -8737,12 +8739,12 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
@@ -8753,16 +8755,16 @@
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O113" s="16" t="n">
         <v>0</v>
@@ -8774,22 +8776,22 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8802,7 +8804,7 @@
       </c>
       <c r="G114" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H114" s="14" t="inlineStr">
@@ -8812,21 +8814,29 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L114" s="14" t="inlineStr"/>
-      <c r="M114" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L114" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M114" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O114" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="15" t="n">
@@ -8836,22 +8846,22 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8874,25 +8884,17 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K115" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="L115" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M115" s="11" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+      <c r="L115" s="11" t="inlineStr"/>
+      <c r="M115" s="11" t="inlineStr"/>
       <c r="N115" s="12" t="n">
         <v>0</v>
       </c>
@@ -8906,22 +8908,22 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -8944,17 +8946,25 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L116" s="14" t="inlineStr"/>
-      <c r="M116" s="14" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L116" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M116" s="14" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N116" s="15" t="n">
         <v>0</v>
       </c>
@@ -8968,22 +8978,22 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9006,11 +9016,11 @@
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K117" s="11" t="n">
         <v>0.5</v>
@@ -9030,12 +9040,12 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
@@ -9045,7 +9055,7 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9058,7 +9068,7 @@
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H118" s="14" t="inlineStr">
@@ -9068,25 +9078,17 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L118" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M118" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L118" s="14" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
       <c r="N118" s="15" t="n">
         <v>0</v>
       </c>
@@ -9100,22 +9102,22 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9128,17 +9130,17 @@
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
@@ -9149,12 +9151,12 @@
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-27990</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>406296</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
@@ -9170,12 +9172,12 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -9185,7 +9187,7 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9208,17 +9210,25 @@
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L120" s="14" t="inlineStr"/>
-      <c r="M120" s="14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L120" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M120" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N120" s="15" t="n">
         <v>0</v>
       </c>
@@ -9232,28 +9242,26 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v/>
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
@@ -9267,7 +9275,7 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
@@ -9279,7 +9287,7 @@
         <v>35</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L121" s="11" t="inlineStr"/>
       <c r="M121" s="11" t="inlineStr"/>
@@ -9296,23 +9304,27 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C122" s="14" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F122" s="14" t="inlineStr">
@@ -9327,19 +9339,19 @@
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="L122" s="14" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -9356,27 +9368,23 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
-        </is>
-      </c>
-      <c r="C123" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr"/>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>Montée de version + Pastell</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr">
@@ -9391,19 +9399,19 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="L123" s="11" t="inlineStr"/>
       <c r="M123" s="11" t="inlineStr"/>
@@ -9420,21 +9428,29 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C124" s="14" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E124" s="14" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F124" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9442,17 +9458,21 @@
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H124" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H124" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K124" s="14" t="n">
         <v>0.5</v>
@@ -9472,18 +9492,18 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr"/>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr"/>
@@ -9500,14 +9520,14 @@
       <c r="H125" s="11" t="inlineStr"/>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L125" s="11" t="inlineStr"/>
       <c r="M125" s="11" t="inlineStr"/>
@@ -9522,31 +9542,83 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="17" t="inlineStr">
+      <c r="A126" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1320</t>
+        </is>
+      </c>
+      <c r="B126" s="14" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="C126" s="14" t="inlineStr"/>
+      <c r="D126" s="14" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="inlineStr"/>
+      <c r="F126" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H126" s="14" t="inlineStr"/>
+      <c r="I126" s="14" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="J126" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L126" s="14" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+      <c r="N126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B126" s="17" t="inlineStr"/>
-      <c r="C126" s="17" t="inlineStr"/>
-      <c r="D126" s="17" t="inlineStr"/>
-      <c r="E126" s="17" t="inlineStr"/>
-      <c r="F126" s="17" t="inlineStr"/>
-      <c r="G126" s="17" t="inlineStr"/>
-      <c r="H126" s="17" t="inlineStr"/>
-      <c r="I126" s="17" t="inlineStr"/>
-      <c r="J126" s="17" t="inlineStr"/>
-      <c r="K126" s="17" t="inlineStr"/>
-      <c r="L126" s="17" t="inlineStr"/>
-      <c r="M126" s="17" t="inlineStr"/>
-      <c r="N126" s="18" t="n">
+      <c r="B127" s="17" t="inlineStr"/>
+      <c r="C127" s="17" t="inlineStr"/>
+      <c r="D127" s="17" t="inlineStr"/>
+      <c r="E127" s="17" t="inlineStr"/>
+      <c r="F127" s="17" t="inlineStr"/>
+      <c r="G127" s="17" t="inlineStr"/>
+      <c r="H127" s="17" t="inlineStr"/>
+      <c r="I127" s="17" t="inlineStr"/>
+      <c r="J127" s="17" t="inlineStr"/>
+      <c r="K127" s="17" t="inlineStr"/>
+      <c r="L127" s="17" t="inlineStr"/>
+      <c r="M127" s="17" t="inlineStr"/>
+      <c r="N127" s="18" t="n">
         <v>62494.694</v>
       </c>
-      <c r="O126" s="18" t="n">
+      <c r="O127" s="18" t="n">
         <v>4805.849999999999</v>
       </c>
-      <c r="P126" s="18" t="n">
-        <v>31.21</v>
+      <c r="P127" s="18" t="n">
+        <v>30.13</v>
       </c>
     </row>
   </sheetData>
@@ -9673,6 +9745,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10247,16 +10320,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>115.5</v>
+        <v>119.75</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>144.5</v>
+        <v>150</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>52.75</v>
@@ -10266,7 +10339,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>24.9%</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10381,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>67.25</v>
+        <v>69.75</v>
       </c>
     </row>
   </sheetData>
@@ -10472,17 +10545,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -10496,7 +10569,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 9 commande(s)</t>
+          <t>Épics créées ce mois — 10 commande(s)</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10624,12 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35114</t>
+          <t>PDMDEP-35139</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-35130</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -10566,7 +10639,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>COMMUNE DE HARNES</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -10586,22 +10659,22 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>00178806</t>
+          <t>00178821</t>
         </is>
       </c>
       <c r="I5" s="25" t="n">
-        <v>985</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35088</t>
+          <t>PDMDEP-35114</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35082</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -10611,7 +10684,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>FREJUS</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -10631,32 +10704,32 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00152501</t>
+          <t>00178806</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>3541.5</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35008</t>
+          <t>PDMDEP-35088</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35000</t>
+          <t>PDMDEP-35082</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
+          <t>FREJUS</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -10666,7 +10739,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -10676,32 +10749,32 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00178436</t>
+          <t>00152501</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>500</v>
+        <v>3541.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34961</t>
+          <t>PDMDEP-35008</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34953</t>
+          <t>PDMDEP-35000</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAIE-MAHAULT</t>
+          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -10721,37 +10794,37 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00178176</t>
+          <t>00178436</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>4050</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35041</t>
+          <t>PDMDEP-34961</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-34953</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>COMMUNE DE BAIE-MAHAULT</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -10766,32 +10839,32 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00178778</t>
+          <t>00178176</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>0</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34993</t>
+          <t>PDMDEP-35041</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34989</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -10811,32 +10884,32 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00178306</t>
+          <t>00178778</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-34993</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-34989</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -10856,22 +10929,22 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178306</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34970</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34966</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -10881,7 +10954,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -10901,83 +10974,107 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00146508</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-34970</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34966</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Commune de Villeneuve D'Ascq</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>00146508</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-34929</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-34925</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>00178034</t>
         </is>
       </c>
-      <c r="I13" s="25" t="n">
+      <c r="I14" s="26" t="n">
         <v>2300</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>9 commande(s)</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="n">
-        <v>15076</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B15" s="17" t="n"/>
@@ -10988,17 +11085,17 @@
       <c r="G15" s="17" t="n"/>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>5 commande(s)</t>
+          <t>10 commande(s)</t>
         </is>
       </c>
       <c r="I15" s="24" t="n">
-        <v>6000</v>
+        <v>15076</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B16" s="17" t="n"/>
@@ -11009,10 +11106,31 @@
       <c r="G16" s="17" t="n"/>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>4 commande(s)</t>
+          <t>5 commande(s)</t>
         </is>
       </c>
       <c r="I16" s="24" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="17" t="n"/>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>5 commande(s)</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="n">
         <v>9076</v>
       </c>
     </row>
